--- a/data/trans_orig/IP2001-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2001-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>18249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13421</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14058</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>27424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109793</t>
+          <t>109424</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120475</t>
+          <t>120287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128003</t>
+          <t>128154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136919</t>
+          <t>136586</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>241477</t>
+          <t>241673</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255039</t>
+          <t>255646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24436</t>
+          <t>25133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26814</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45642</t>
+          <t>46893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160695</t>
+          <t>159998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172850</t>
+          <t>172784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175363</t>
+          <t>175368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>188734</t>
+          <t>189360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>341666</t>
+          <t>340415</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>358990</t>
+          <t>358435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26179</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115641</t>
+          <t>115860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125123</t>
+          <t>125306</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123193</t>
+          <t>122795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133252</t>
+          <t>132778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242878</t>
+          <t>242087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>255544</t>
+          <t>255647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23225</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24187</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43498</t>
+          <t>41887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175612</t>
+          <t>174921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188201</t>
+          <t>188431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171847</t>
+          <t>171515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184628</t>
+          <t>184474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>350421</t>
+          <t>352032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>369732</t>
+          <t>370683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43146</t>
+          <t>43502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66270</t>
+          <t>66367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43736</t>
+          <t>43372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67227</t>
+          <t>66992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93664</t>
+          <t>92812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124699</t>
+          <t>124278</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>575579</t>
+          <t>575482</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>598703</t>
+          <t>598347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>610304</t>
+          <t>610539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>633795</t>
+          <t>634159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1194682</t>
+          <t>1195103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1225717</t>
+          <t>1226569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20285</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23431</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>21856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39754</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112883</t>
+          <t>112609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124924</t>
+          <t>124840</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118696</t>
+          <t>119282</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131534</t>
+          <t>131538</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235541</t>
+          <t>235714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>254336</t>
+          <t>253439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28383</t>
+          <t>28679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26389</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30617</t>
+          <t>30252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50667</t>
+          <t>50615</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>161312</t>
+          <t>161016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175346</t>
+          <t>174965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>185696</t>
+          <t>184710</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199314</t>
+          <t>198924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>351113</t>
+          <t>351165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371163</t>
+          <t>371528</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24595</t>
+          <t>24570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23607</t>
+          <t>24610</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39979</t>
+          <t>41873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123934</t>
+          <t>123384</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135180</t>
+          <t>134736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127698</t>
+          <t>127723</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140636</t>
+          <t>140480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>256972</t>
+          <t>255078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273344</t>
+          <t>272341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20975</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36423</t>
+          <t>37769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171291</t>
+          <t>171698</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184306</t>
+          <t>184196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173384</t>
+          <t>173461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185953</t>
+          <t>186393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>349636</t>
+          <t>348290</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367673</t>
+          <t>367255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51020</t>
+          <t>49264</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77399</t>
+          <t>74585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53595</t>
+          <t>54990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80425</t>
+          <t>81579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109273</t>
+          <t>112165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147774</t>
+          <t>147484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>581822</t>
+          <t>584636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608201</t>
+          <t>609957</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>620439</t>
+          <t>619285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>647269</t>
+          <t>645874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1212311</t>
+          <t>1212601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1250812</t>
+          <t>1247920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21759</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36887</t>
+          <t>37613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103274</t>
+          <t>103473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115351</t>
+          <t>115740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117351</t>
+          <t>117389</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129555</t>
+          <t>129802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>225862</t>
+          <t>225136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242566</t>
+          <t>242698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31253</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21757</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47177</t>
+          <t>48149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>163310</t>
+          <t>163945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178573</t>
+          <t>178180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188276</t>
+          <t>187664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200166</t>
+          <t>199916</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>357419</t>
+          <t>356447</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375980</t>
+          <t>375226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>20515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24551</t>
+          <t>24899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23518</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40764</t>
+          <t>40396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>127778</t>
+          <t>127652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138808</t>
+          <t>139150</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135876</t>
+          <t>135528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149359</t>
+          <t>148735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>267830</t>
+          <t>268198</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285076</t>
+          <t>284994</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12780</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27675</t>
+          <t>27694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52315</t>
+          <t>50797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164808</t>
+          <t>164789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179703</t>
+          <t>179678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160742</t>
+          <t>159173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176194</t>
+          <t>174841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330203</t>
+          <t>331721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351243</t>
+          <t>351417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57365</t>
+          <t>57351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83173</t>
+          <t>81317</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55615</t>
+          <t>55501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82868</t>
+          <t>82084</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120256</t>
+          <t>119580</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155821</t>
+          <t>153733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>575679</t>
+          <t>577535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>601487</t>
+          <t>601501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>616737</t>
+          <t>617521</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>643990</t>
+          <t>644104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1202636</t>
+          <t>1204724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1238201</t>
+          <t>1238877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103727</t>
+          <t>103328</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111806</t>
+          <t>111659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123695</t>
+          <t>123600</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133642</t>
+          <t>133587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231234</t>
+          <t>230900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243601</t>
+          <t>243531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>28208</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>20716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39268</t>
+          <t>40506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171704</t>
+          <t>171298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181328</t>
+          <t>181088</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218479</t>
+          <t>219453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235309</t>
+          <t>234745</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>394772</t>
+          <t>393534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>413720</t>
+          <t>413324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173088</t>
+          <t>174310</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183399</t>
+          <t>184133</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169005</t>
+          <t>168379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179657</t>
+          <t>179435</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>346585</t>
+          <t>347599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>361662</t>
+          <t>361718</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>24244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155542</t>
+          <t>155570</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162963</t>
+          <t>163204</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160773</t>
+          <t>159911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173006</t>
+          <t>172773</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>319254</t>
+          <t>318999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>334328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57334</t>
+          <t>57977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58646</t>
+          <t>59127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>89761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615409</t>
+          <t>616395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>633855</t>
+          <t>634145</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>688650</t>
+          <t>688007</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>712645</t>
+          <t>713267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1310937</t>
+          <t>1310618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341733</t>
+          <t>1341252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2001-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2001-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8221</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13817</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11595</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7386</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18249</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6360</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17201</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8221</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4838</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13270</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27424</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>133203</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>127607</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>136721</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>116078</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>109424</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>120287</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>110472</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>121313</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>133203</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>128154</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>136586</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>241673</t>
+          <t>241355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255646</t>
+          <t>255546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>141424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>141424</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>141424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>127673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>127673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>127673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>141424</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>141424</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>141424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19456</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13422</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27113</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>17544</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12347</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25133</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12581</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24678</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19456</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12817</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26809</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28873</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46893</t>
+          <t>47193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>182721</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>175064</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>188755</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>167587</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>159998</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>172784</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>160453</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>172550</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>182721</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>175368</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>189360</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,38%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>340415</t>
+          <t>340115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>358435</t>
+          <t>357927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>202177</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>202177</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>202177</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185131</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185131</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185131</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>202177</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>202177</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>202177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10138</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5940</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15955</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8946</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4892</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14338</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5380</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14724</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10138</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6081</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16064</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>25672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>128721</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>122904</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>132919</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>121252</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>115860</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>125306</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>115474</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>124818</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>128721</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>122795</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>132778</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242087</t>
+          <t>243385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>255647</t>
+          <t>255950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>138859</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>138859</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>138859</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>130198</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>130198</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>130198</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>138859</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>138859</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>138859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16272</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10845</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23016</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>16092</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10416</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23926</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9892</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23406</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16272</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10598</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23557</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41887</t>
+          <t>43260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>178800</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>172056</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>184227</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>182755</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>174921</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>188431</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>175441</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>188955</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,76%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>178800</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>171515</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>184474</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>352032</t>
+          <t>350659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>370683</t>
+          <t>369289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>195072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>195072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>195072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>198847</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>198847</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>198847</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>195072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>195072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>195072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2100,67 +2100,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>44124</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>65847</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>54177</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>43502</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>66367</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>43339</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>66323</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,44%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>54087</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>43372</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>66992</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92812</t>
+          <t>93753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124278</t>
+          <t>124607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>623444</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>611684</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>633407</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>877</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>587672</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>575482</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>598347</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>575526</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>598510</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,56%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>623444</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>610539</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>634159</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1195103</t>
+          <t>1194774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1226569</t>
+          <t>1225628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>677531</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>677531</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>677531</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>958</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>641849</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>641849</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>641849</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1019</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>677531</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>677531</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>677531</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16182</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10068</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22935</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13362</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8328</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20559</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8568</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19968</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10,03%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16182</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10589</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>22845</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21856</t>
+          <t>21510</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>39848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>125945</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>119192</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>132059</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>119806</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>112609</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>124840</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>113200</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>124600</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>89,97%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>125945</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>119282</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>131538</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235714</t>
+          <t>235447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>253439</t>
+          <t>253785</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>142127</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>142127</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>142127</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>142127</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>142127</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>142127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19136</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13276</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26872</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>20879</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14730</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28679</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14754</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>28619</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,01%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19136</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13161</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>27375</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30252</t>
+          <t>30513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50615</t>
+          <t>50159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>192949</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>185213</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>198809</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>168816</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>161016</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>174965</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>161076</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>174941</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,99%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>192949</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>184710</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>198924</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,98%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>351165</t>
+          <t>351621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371528</t>
+          <t>371267</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212085</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212085</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212085</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>189695</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>189695</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>189695</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212085</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212085</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17032</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24289</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14669</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9922</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21274</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9592</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21336</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,14%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17032</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11813</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24570</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>23186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41873</t>
+          <t>40491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>135261</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>128004</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140968</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,05%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>129989</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>123384</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134736</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>123322</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>135066</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,86%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>135261</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>127723</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>140480</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255078</t>
+          <t>256460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272341</t>
+          <t>273765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,67 +3704,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>13607</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7991</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21393</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>12586</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20002</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7757</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19562</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,57%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13607</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7966</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20898</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37769</t>
+          <t>35995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>180752</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>172966</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>186368</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>179114</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>171698</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>184196</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>172138</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>183943</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,43%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,57%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>180752</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>173461</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>186393</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>348290</t>
+          <t>350064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367255</t>
+          <t>368047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>194359</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>194359</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>194359</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>191700</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>191700</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>191700</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>194359</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>194359</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>194359</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53823</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>79914</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>61495</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49264</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>74585</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>48968</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>72618</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>65958</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>54990</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>81579</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112165</t>
+          <t>110538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147484</t>
+          <t>146710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>634906</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>620950</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>647041</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>861</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>597726</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>584636</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>609957</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>586603</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>610253</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>634906</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>619285</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>645874</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1212601</t>
+          <t>1213375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1247920</t>
+          <t>1249547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700864</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700864</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700864</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>949</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>659221</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>659221</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>659221</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>700864</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>700864</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>700864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4622,67 +4622,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>14446</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9135</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21616</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>13060</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7899</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20166</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8185</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20436</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10,56%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14446</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9308</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21721</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37613</t>
+          <t>36651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124664</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>117494</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>129975</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,43%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>110579</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>103473</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>115740</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>103203</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>115454</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>89,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124664</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>117389</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>129802</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,62%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>225136</t>
+          <t>226098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242698</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>123639</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>123639</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>123639</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15380</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9880</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22346</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>22539</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16383</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>30618</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15767</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29782</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15380</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10117</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22369</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>29393</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48149</t>
+          <t>47976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>194653</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>187687</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>200153</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>172024</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>163945</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>178180</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>164781</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>178796</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>194653</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>187664</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>199916</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>356447</t>
+          <t>356620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375226</t>
+          <t>375203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210033</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210033</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210033</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>194563</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>194563</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>194563</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210033</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210033</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210033</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16962</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11587</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24662</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14514</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9017</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20515</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9761</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21015</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,8%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16962</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11692</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24899</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>23909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40396</t>
+          <t>40015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>143465</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>135765</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148840</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>133653</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127652</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>139150</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>127152</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>138406</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,2%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>143465</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>135528</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>148735</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>268198</t>
+          <t>268579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284994</t>
+          <t>284685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21165</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14577</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28763</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19069</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12805</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27694</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12738</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27558</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>21165</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15194</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>30862</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50797</t>
+          <t>50421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>168870</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>161272</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>175458</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>173414</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>164789</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>179678</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>164925</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>179745</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,09%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,35%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>168870</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>159173</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>174841</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331721</t>
+          <t>332097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351417</t>
+          <t>351964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>190035</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>190035</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>190035</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>190035</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>190035</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>190035</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>55272</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>81936</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>69182</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>57351</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>81317</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>56179</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>82855</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67954</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>55501</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>82084</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119580</t>
+          <t>119570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153733</t>
+          <t>157149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>631651</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>617669</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>644333</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>885</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>589670</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>577535</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>601501</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>575997</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>602673</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>631651</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>617521</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>644104</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1204724</t>
+          <t>1201308</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1238877</t>
+          <t>1238887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699605</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699605</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699605</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>989</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>658852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>658852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>658852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>998</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>699605</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>699605</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>699605</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6182</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2987</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11982</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6448</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3411</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11742</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13157</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>116697</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>110897</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>119892</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>108622</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>103328</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>111659</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>94,4%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>129821</t>
+          <t>112484</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123600</t>
+          <t>106818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133587</t>
+          <t>115630</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>238443</t>
+          <t>229180</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230900</t>
+          <t>221978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243531</t>
+          <t>234195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18261</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11623</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27465</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9197</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5291</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15081</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28208</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28867</t>
+          <t>27082</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40506</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>212800</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>203596</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>219438</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>177182</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>171298</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>181088</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,07%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>227991</t>
+          <t>172411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219453</t>
+          <t>167123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234745</t>
+          <t>176434</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>405173</t>
+          <t>385211</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>393534</t>
+          <t>375478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>413324</t>
+          <t>393169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186379</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186379</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186379</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247661</t>
+          <t>181232</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247661</t>
+          <t>181232</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247661</t>
+          <t>181232</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>434040</t>
+          <t>412293</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>434040</t>
+          <t>412293</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>434040</t>
+          <t>412293</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8470</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4236</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15140</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7717</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3433</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13256</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>179849</t>
+          <t>158677</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174310</t>
+          <t>152007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184133</t>
+          <t>162911</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>175369</t>
+          <t>146505</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>168379</t>
+          <t>140918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179435</t>
+          <t>150146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>355218</t>
+          <t>305183</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>347599</t>
+          <t>298249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>361718</t>
+          <t>311423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>187566</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>187566</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>187566</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154306</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154306</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154306</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371269</t>
+          <t>321454</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371269</t>
+          <t>321454</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371269</t>
+          <t>321454</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9588</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4698</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17052</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5092</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2176</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9810</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,27 +7668,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14674</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24244</t>
+          <t>23376</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>157020</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149556</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>161910</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>160288</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>155570</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>163204</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>168045</t>
+          <t>159491</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159911</t>
+          <t>153569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172773</t>
+          <t>162373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,22 +7781,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>328333</t>
+          <t>316510</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>318999</t>
+          <t>307808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334328</t>
+          <t>322003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>165380</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>165380</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>165380</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>164576</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>164576</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>164576</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>343243</t>
+          <t>331184</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>343243</t>
+          <t>331184</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>343243</t>
+          <t>331184</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42502</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31994</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56115</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>28454</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20251</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>38001</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32717</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57977</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>71027</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59127</t>
+          <t>57801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89761</t>
+          <t>87760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>645193</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>631580</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>655701</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>874</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>625942</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>616395</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>634145</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>701226</t>
+          <t>590891</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>688007</t>
+          <t>581656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>713267</t>
+          <t>598893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1327167</t>
+          <t>1236084</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1310618</t>
+          <t>1219351</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341252</t>
+          <t>1249310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>687695</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>687695</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>687695</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>918</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>654396</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>654396</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>654396</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>745984</t>
+          <t>619416</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>745984</t>
+          <t>619416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>745984</t>
+          <t>619416</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1400379</t>
+          <t>1307111</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1400379</t>
+          <t>1307111</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1400379</t>
+          <t>1307111</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
